--- a/config/xlsx/cultivation.xlsx
+++ b/config/xlsx/cultivation.xlsx
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>6000</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>8000</v>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>10000</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>15000</v>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>17000</v>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>20000</v>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>900</v>
+        <v>910</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>153200</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2150</v>
+        <v>2166</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>200000</v>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3900</v>
+        <v>3895</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>400000</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6300</v>
+        <v>6288</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>4792200</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>13600</v>
+        <v>13617</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>8000000</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>4700</v>
+        <v>4698</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>421700300</v>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>13700</v>
+        <v>13680</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>500000000</v>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>31000</v>
+        <v>31020</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1000000000</v>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>99999999</v>
+        <v>100000026</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>454136600</v>
